--- a/code/cmb/highl_litebird_fisher.xlsx
+++ b/code/cmb/highl_litebird_fisher.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,34 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5107474.980136095</v>
+        <v>1534250.365740143</v>
       </c>
       <c r="C2" t="n">
-        <v>-8201923.108000796</v>
+        <v>-2465789.007067145</v>
       </c>
       <c r="D2" t="n">
-        <v>4373827.615629417</v>
+        <v>1313360.706093156</v>
       </c>
       <c r="E2" t="n">
-        <v>772652.3802493648</v>
+        <v>232978.5477285732</v>
       </c>
       <c r="F2" t="n">
-        <v>-1894035.861807088</v>
+        <v>-569200.7125255676</v>
       </c>
       <c r="G2" t="n">
-        <v>-513264.7674707776</v>
+        <v>-154254.7441250013</v>
       </c>
       <c r="H2" t="n">
-        <v>-165349.0563685114</v>
+        <v>-49660.04353414954</v>
       </c>
       <c r="I2" t="n">
-        <v>1525365.051990126</v>
+        <v>458351.5773539537</v>
       </c>
       <c r="J2" t="n">
-        <v>-327952.4580514712</v>
+        <v>-98647.72381336358</v>
       </c>
       <c r="K2" t="n">
-        <v>-102069.4611897737</v>
+        <v>-30698.91040770178</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-8201923.108000796</v>
+        <v>-2465789.007067145</v>
       </c>
       <c r="C3" t="n">
-        <v>26223604.52020243</v>
+        <v>7880694.603009514</v>
       </c>
       <c r="D3" t="n">
-        <v>-6154905.210216631</v>
+        <v>-1849633.549529412</v>
       </c>
       <c r="E3" t="n">
-        <v>-1139493.513526164</v>
+        <v>-344860.4661014363</v>
       </c>
       <c r="F3" t="n">
-        <v>2630138.491187462</v>
+        <v>791578.9405833196</v>
       </c>
       <c r="G3" t="n">
-        <v>632634.1717947938</v>
+        <v>190494.6875722898</v>
       </c>
       <c r="H3" t="n">
-        <v>319385.2318897443</v>
+        <v>95961.06646531745</v>
       </c>
       <c r="I3" t="n">
-        <v>-2122046.095225201</v>
+        <v>-638509.6166821993</v>
       </c>
       <c r="J3" t="n">
-        <v>108969.7962308324</v>
+        <v>33354.36198415331</v>
       </c>
       <c r="K3" t="n">
-        <v>48038.59561283697</v>
+        <v>14609.52517085201</v>
       </c>
     </row>
     <row r="4">
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4373827.615629417</v>
+        <v>1313360.706093156</v>
       </c>
       <c r="C4" t="n">
-        <v>-6154905.210216631</v>
+        <v>-1849633.549529412</v>
       </c>
       <c r="D4" t="n">
-        <v>3852904.092829962</v>
+        <v>1156611.444185983</v>
       </c>
       <c r="E4" t="n">
-        <v>641466.5169948733</v>
+        <v>193148.1385056295</v>
       </c>
       <c r="F4" t="n">
-        <v>-1606625.165140122</v>
+        <v>-482582.1664740651</v>
       </c>
       <c r="G4" t="n">
-        <v>-437412.7849100615</v>
+        <v>-131388.523048574</v>
       </c>
       <c r="H4" t="n">
-        <v>-141825.2555552242</v>
+        <v>-42581.49467036214</v>
       </c>
       <c r="I4" t="n">
-        <v>1293773.427538889</v>
+        <v>388576.3303657197</v>
       </c>
       <c r="J4" t="n">
-        <v>-282290.5411773181</v>
+        <v>-84841.5244460473</v>
       </c>
       <c r="K4" t="n">
-        <v>-87685.60181138761</v>
+        <v>-26351.78098758115</v>
       </c>
     </row>
     <row r="5">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>772652.3802493648</v>
+        <v>232978.5477285732</v>
       </c>
       <c r="C5" t="n">
-        <v>-1139493.513526165</v>
+        <v>-344860.4661014363</v>
       </c>
       <c r="D5" t="n">
-        <v>641466.5169948733</v>
+        <v>193148.1385056295</v>
       </c>
       <c r="E5" t="n">
-        <v>153149.8364274892</v>
+        <v>46691.28872758696</v>
       </c>
       <c r="F5" t="n">
-        <v>-308833.9129861366</v>
+        <v>-93260.85407623119</v>
       </c>
       <c r="G5" t="n">
-        <v>-86139.02835270095</v>
+        <v>-26012.07860153096</v>
       </c>
       <c r="H5" t="n">
-        <v>-23249.94598476141</v>
+        <v>-7006.296166361364</v>
       </c>
       <c r="I5" t="n">
-        <v>248080.1502674297</v>
+        <v>74886.84147569042</v>
       </c>
       <c r="J5" t="n">
-        <v>-66029.38426162761</v>
+        <v>-19974.91134184857</v>
       </c>
       <c r="K5" t="n">
-        <v>-20038.64388015723</v>
+        <v>-6060.938119579338</v>
       </c>
     </row>
     <row r="6">
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1894035.861807088</v>
+        <v>-569200.7125255676</v>
       </c>
       <c r="C6" t="n">
-        <v>2630138.491187462</v>
+        <v>791578.9405833196</v>
       </c>
       <c r="D6" t="n">
-        <v>-1606625.165140122</v>
+        <v>-482582.1664740651</v>
       </c>
       <c r="E6" t="n">
-        <v>-308833.9129861366</v>
+        <v>-93260.85407623119</v>
       </c>
       <c r="F6" t="n">
-        <v>771920.9888792145</v>
+        <v>232079.7269377884</v>
       </c>
       <c r="G6" t="n">
-        <v>213876.5088688827</v>
+        <v>64303.23682742559</v>
       </c>
       <c r="H6" t="n">
-        <v>55383.14905513128</v>
+        <v>16641.52124632207</v>
       </c>
       <c r="I6" t="n">
-        <v>-621278.5533734449</v>
+        <v>-186763.6910478294</v>
       </c>
       <c r="J6" t="n">
-        <v>163039.2472315809</v>
+        <v>49047.43526750131</v>
       </c>
       <c r="K6" t="n">
-        <v>49546.64184895738</v>
+        <v>14904.33923996635</v>
       </c>
     </row>
     <row r="7">
@@ -672,34 +672,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-513264.7674707776</v>
+        <v>-154254.7441250013</v>
       </c>
       <c r="C7" t="n">
-        <v>632634.1717947938</v>
+        <v>190494.6875722898</v>
       </c>
       <c r="D7" t="n">
-        <v>-437412.7849100615</v>
+        <v>-131388.523048574</v>
       </c>
       <c r="E7" t="n">
-        <v>-86139.02835270095</v>
+        <v>-26012.07860153096</v>
       </c>
       <c r="F7" t="n">
-        <v>213876.5088688827</v>
+        <v>64303.23682742559</v>
       </c>
       <c r="G7" t="n">
-        <v>59966.87061477369</v>
+        <v>18029.20801028038</v>
       </c>
       <c r="H7" t="n">
-        <v>14452.94309386293</v>
+        <v>4343.231724069689</v>
       </c>
       <c r="I7" t="n">
-        <v>-172121.4681091689</v>
+        <v>-51742.47379161995</v>
       </c>
       <c r="J7" t="n">
-        <v>48312.4360050785</v>
+        <v>14531.7832049718</v>
       </c>
       <c r="K7" t="n">
-        <v>14577.45030482501</v>
+        <v>4384.544221112774</v>
       </c>
     </row>
     <row r="8">
@@ -709,34 +709,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-165349.0563685114</v>
+        <v>-49660.04353414954</v>
       </c>
       <c r="C8" t="n">
-        <v>319385.2318897442</v>
+        <v>95961.06646531745</v>
       </c>
       <c r="D8" t="n">
-        <v>-141825.2555552242</v>
+        <v>-42581.49467036214</v>
       </c>
       <c r="E8" t="n">
-        <v>-23249.94598476141</v>
+        <v>-7006.296166361364</v>
       </c>
       <c r="F8" t="n">
-        <v>55383.14905513128</v>
+        <v>16641.52124632207</v>
       </c>
       <c r="G8" t="n">
-        <v>14452.94309386293</v>
+        <v>4343.231724069689</v>
       </c>
       <c r="H8" t="n">
-        <v>5933.675440229372</v>
+        <v>1781.676765714834</v>
       </c>
       <c r="I8" t="n">
-        <v>-44619.8079945415</v>
+        <v>-13405.70101155673</v>
       </c>
       <c r="J8" t="n">
-        <v>6599.165087879396</v>
+        <v>1986.54938937073</v>
       </c>
       <c r="K8" t="n">
-        <v>2175.404601428579</v>
+        <v>654.6553339487015</v>
       </c>
     </row>
     <row r="9">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1525365.051990126</v>
+        <v>458351.5773539537</v>
       </c>
       <c r="C9" t="n">
-        <v>-2122046.095225201</v>
+        <v>-638509.6166821993</v>
       </c>
       <c r="D9" t="n">
-        <v>1293773.427538889</v>
+        <v>388576.3303657197</v>
       </c>
       <c r="E9" t="n">
-        <v>248080.1502674297</v>
+        <v>74886.84147569042</v>
       </c>
       <c r="F9" t="n">
-        <v>-621278.5533734449</v>
+        <v>-186763.6910478294</v>
       </c>
       <c r="G9" t="n">
-        <v>-172121.4681091689</v>
+        <v>-51742.47379161995</v>
       </c>
       <c r="H9" t="n">
-        <v>-44619.8079945415</v>
+        <v>-13405.70101155673</v>
       </c>
       <c r="I9" t="n">
-        <v>500140.6547938203</v>
+        <v>150329.9041706838</v>
       </c>
       <c r="J9" t="n">
-        <v>-131069.4041827944</v>
+        <v>-39423.93954933473</v>
       </c>
       <c r="K9" t="n">
-        <v>-39837.20286680517</v>
+        <v>-11981.80793411148</v>
       </c>
     </row>
     <row r="10">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-327952.4580514712</v>
+        <v>-98647.72381336358</v>
       </c>
       <c r="C10" t="n">
-        <v>108969.7962308324</v>
+        <v>33354.36198415331</v>
       </c>
       <c r="D10" t="n">
-        <v>-282290.5411773181</v>
+        <v>-84841.5244460473</v>
       </c>
       <c r="E10" t="n">
-        <v>-66029.38426162761</v>
+        <v>-19974.91134184857</v>
       </c>
       <c r="F10" t="n">
-        <v>163039.2472315809</v>
+        <v>49047.43526750131</v>
       </c>
       <c r="G10" t="n">
-        <v>48312.4360050785</v>
+        <v>14531.7832049718</v>
       </c>
       <c r="H10" t="n">
-        <v>6599.165087879397</v>
+        <v>1986.54938937073</v>
       </c>
       <c r="I10" t="n">
-        <v>-131069.4041827944</v>
+        <v>-39423.93954933473</v>
       </c>
       <c r="J10" t="n">
-        <v>49996.54499540891</v>
+        <v>15036.74041933896</v>
       </c>
       <c r="K10" t="n">
-        <v>14675.06798284245</v>
+        <v>4413.716456276799</v>
       </c>
     </row>
     <row r="11">
@@ -820,34 +820,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-102069.4611897737</v>
+        <v>-30698.91040770178</v>
       </c>
       <c r="C11" t="n">
-        <v>48038.59561283698</v>
+        <v>14609.525170852</v>
       </c>
       <c r="D11" t="n">
-        <v>-87685.60181138761</v>
+        <v>-26351.78098758115</v>
       </c>
       <c r="E11" t="n">
-        <v>-20038.64388015723</v>
+        <v>-6060.938119579338</v>
       </c>
       <c r="F11" t="n">
-        <v>49546.64184895738</v>
+        <v>14904.33923996635</v>
       </c>
       <c r="G11" t="n">
-        <v>14577.45030482501</v>
+        <v>4384.544221112774</v>
       </c>
       <c r="H11" t="n">
-        <v>2175.404601428579</v>
+        <v>654.6553339487015</v>
       </c>
       <c r="I11" t="n">
-        <v>-39837.20286680517</v>
+        <v>-11981.80793411148</v>
       </c>
       <c r="J11" t="n">
-        <v>14675.06798284245</v>
+        <v>4413.716456276799</v>
       </c>
       <c r="K11" t="n">
-        <v>4319.365283735996</v>
+        <v>1299.129005943477</v>
       </c>
     </row>
   </sheetData>
